--- a/25-11-pdf-Analyzer/analyse_ergebnisse_v4-Mathbuch1.xlsx
+++ b/25-11-pdf-Analyzer/analyse_ergebnisse_v4-Mathbuch1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/131a8beddc4e0454/01JupyterAndCo/04GitHub/GitHubCloneMBP/richard4231.github.io/25-11-pdf-Analyzer/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/131a8beddc4e0454/01JupyterAndCo/04GitHub/GitHubCloneMac/richard4231.github.io/25-11-pdf-Analyzer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="336" documentId="8_{520C6DA0-CDB0-624A-9949-4D5B6898A185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A5498FC5-2D43-2E41-96DD-64432A8C4C2A}"/>
+  <xr:revisionPtr revIDLastSave="349" documentId="8_{520C6DA0-CDB0-624A-9949-4D5B6898A185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B95C6D3-2903-574F-BFB6-89699A7B38D5}"/>
   <bookViews>
-    <workbookView xWindow="500" yWindow="680" windowWidth="26040" windowHeight="15240" xr2:uid="{F946418D-52D0-4E49-9A8C-9784AA1B6916}"/>
+    <workbookView xWindow="17720" yWindow="5680" windowWidth="26040" windowHeight="15240" xr2:uid="{F946418D-52D0-4E49-9A8C-9784AA1B6916}"/>
   </bookViews>
   <sheets>
     <sheet name="analyse_ergebnisse_v4-Mathbuch1" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6443" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6444" uniqueCount="167">
   <si>
     <t>PDF</t>
   </si>
@@ -556,6 +556,9 @@
   </si>
   <si>
     <t>ohne BNE-Bezug</t>
+  </si>
+  <si>
+    <t>Reflexionstiefe</t>
   </si>
 </sst>
 </file>
@@ -1055,10 +1058,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
@@ -1107,10 +1109,7 @@
   </cellStyles>
   <dxfs count="4">
     <dxf>
-      <font>
-        <b/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <numFmt numFmtId="164" formatCode="0.0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -1119,7 +1118,10 @@
       <numFmt numFmtId="164" formatCode="0.0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
+      <font>
+        <b/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1163,8 +1165,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{3E2130B6-01EB-504A-A82F-116D857DC737}" name="Tabelle3" displayName="Tabelle3" ref="V1:AD113" totalsRowShown="0">
-  <autoFilter ref="V1:AD113" xr:uid="{3E2130B6-01EB-504A-A82F-116D857DC737}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{3E2130B6-01EB-504A-A82F-116D857DC737}" name="Tabelle3" displayName="Tabelle3" ref="V1:AE113" totalsRowShown="0">
+  <autoFilter ref="V1:AE113" xr:uid="{3E2130B6-01EB-504A-A82F-116D857DC737}">
     <filterColumn colId="1">
       <filters>
         <filter val="1"/>
@@ -1281,17 +1283,17 @@
       </filters>
     </filterColumn>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="V3:AD113">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="V2:AD108">
     <sortCondition descending="1" ref="Z1:Z113"/>
   </sortState>
-  <tableColumns count="9">
+  <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{A0C018C7-F6D1-F841-810B-8A6360183DC9}" name="Seite"/>
-    <tableColumn id="11" xr3:uid="{E0FED4AD-0AF3-6D4D-82A4-118DC92CC3B4}" name="Schulbuchseite" dataDxfId="0">
+    <tableColumn id="11" xr3:uid="{E0FED4AD-0AF3-6D4D-82A4-118DC92CC3B4}" name="Schulbuchseite" dataDxfId="3">
       <calculatedColumnFormula>Tabelle3[[#This Row],[Seite]]-2</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{B8F867EA-5D14-7E4C-8895-3EA33DED557A}" name="Anzahl"/>
     <tableColumn id="3" xr3:uid="{AA9B75F7-387B-2C4D-9051-47B9A42EC4A5}" name="Rang"/>
-    <tableColumn id="4" xr3:uid="{684ACF35-1508-3E48-8C5A-9F196266158C}" name="Summe Score" dataDxfId="3">
+    <tableColumn id="4" xr3:uid="{684ACF35-1508-3E48-8C5A-9F196266158C}" name="Summe Score" dataDxfId="0">
       <calculatedColumnFormula array="1">SUMPRODUCT((Tabelle1[Seite]=V2)*Tabelle1[Score_Gewichtet])</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{4C63FC84-FA0F-B746-B1EA-28FD761487ED}" name="Thema" dataDxfId="2"/>
@@ -1300,6 +1302,7 @@
     <tableColumn id="8" xr3:uid="{9066A753-44BD-564B-BEB0-F50B4A150FF0}" name="ohne BNE-Bezug" dataDxfId="1">
       <calculatedColumnFormula>IF(Tabelle3[[#This Row],[Summe Score]]&lt;5,"x","")</calculatedColumnFormula>
     </tableColumn>
+    <tableColumn id="7" xr3:uid="{69EEEDEB-9D00-BA46-8FD8-CF2615F8C1FF}" name="Reflexionstiefe"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1622,7 +1625,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CAE9259-8FCA-E349-9204-1C51259F460E}">
-  <dimension ref="A1:AD1569"/>
+  <dimension ref="A1:AE1569"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="8" max="8" width="14.1640625" customWidth="1"/>
@@ -1631,7 +1634,7 @@
     <col min="29" max="29" width="4.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1716,8 +1719,11 @@
       <c r="AD1" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="2" spans="1:30" hidden="1" x14ac:dyDescent="0.2">
+      <c r="AE1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1764,29 +1770,28 @@
         <v>111</v>
       </c>
       <c r="V2">
-        <v>1</v>
-      </c>
-      <c r="W2" s="3">
+        <v>30</v>
+      </c>
+      <c r="W2" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
-        <v>-1</v>
+        <v>28</v>
       </c>
       <c r="X2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Y2">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="Z2" s="1" cm="1">
         <f t="array" ref="Z2">SUMPRODUCT((Tabelle1[Seite]=V2)*Tabelle1[Score_Gewichtet])</f>
-        <v>0.1</v>
+        <v>33.950000000000003</v>
       </c>
       <c r="AA2" s="1"/>
-      <c r="AD2" t="str">
-        <f>IF(Tabelle3[[#This Row],[Summe Score]]&lt;5,"x","")</f>
-        <v>x</v>
-      </c>
-    </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AD2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1834,7 +1839,7 @@
       <c r="V3">
         <v>88</v>
       </c>
-      <c r="W3" s="3">
+      <c r="W3" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>86</v>
       </c>
@@ -1854,9 +1859,8 @@
       <c r="AB3" t="s">
         <v>150</v>
       </c>
-      <c r="AD3" s="2"/>
-    </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -1904,7 +1908,7 @@
       <c r="V4">
         <v>16</v>
       </c>
-      <c r="W4" s="3">
+      <c r="W4" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>14</v>
       </c>
@@ -1923,7 +1927,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -1969,28 +1973,28 @@
         <v>65</v>
       </c>
       <c r="V5">
+        <v>89</v>
+      </c>
+      <c r="W5" s="2">
+        <f>Tabelle3[[#This Row],[Seite]]-2</f>
+        <v>87</v>
+      </c>
+      <c r="X5">
         <v>30</v>
       </c>
-      <c r="W5" s="3">
-        <f>Tabelle3[[#This Row],[Seite]]-2</f>
-        <v>28</v>
-      </c>
-      <c r="X5">
-        <v>8</v>
-      </c>
       <c r="Y5">
-        <v>88</v>
+        <v>3</v>
       </c>
       <c r="Z5" s="1" cm="1">
         <f t="array" ref="Z5">SUMPRODUCT((Tabelle1[Seite]=V5)*Tabelle1[Score_Gewichtet])</f>
-        <v>33.950000000000003</v>
+        <v>33.350000000000009</v>
       </c>
       <c r="AA5" s="1"/>
       <c r="AD5" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -2036,28 +2040,28 @@
         <v>55</v>
       </c>
       <c r="V6">
-        <v>89</v>
-      </c>
-      <c r="W6" s="3">
+        <v>109</v>
+      </c>
+      <c r="W6" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="X6">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="Y6">
-        <v>3</v>
+        <v>73</v>
       </c>
       <c r="Z6" s="1" cm="1">
         <f t="array" ref="Z6">SUMPRODUCT((Tabelle1[Seite]=V6)*Tabelle1[Score_Gewichtet])</f>
-        <v>33.350000000000009</v>
+        <v>28.249999999999996</v>
       </c>
       <c r="AA6" s="1"/>
-      <c r="AD6" s="2" t="s">
+      <c r="AD6" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -2105,7 +2109,7 @@
       <c r="V7">
         <v>47</v>
       </c>
-      <c r="W7" s="3">
+      <c r="W7" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>45</v>
       </c>
@@ -2125,9 +2129,8 @@
       <c r="AB7" t="s">
         <v>134</v>
       </c>
-      <c r="AD7" s="2"/>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -2173,28 +2176,28 @@
         <v>47</v>
       </c>
       <c r="V8">
-        <v>109</v>
-      </c>
-      <c r="W8" s="3">
+        <v>79</v>
+      </c>
+      <c r="W8" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="X8">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Y8">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="Z8" s="1" cm="1">
         <f t="array" ref="Z8">SUMPRODUCT((Tabelle1[Seite]=V8)*Tabelle1[Score_Gewichtet])</f>
-        <v>28.249999999999996</v>
+        <v>27.150000000000006</v>
       </c>
       <c r="AA8" s="1"/>
       <c r="AD8" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -2242,7 +2245,7 @@
       <c r="V9">
         <v>31</v>
       </c>
-      <c r="W9" s="3">
+      <c r="W9" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>29</v>
       </c>
@@ -2261,7 +2264,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -2307,28 +2310,28 @@
         <v>65</v>
       </c>
       <c r="V10">
-        <v>79</v>
-      </c>
-      <c r="W10" s="3">
+        <v>4</v>
+      </c>
+      <c r="W10" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
-        <v>77</v>
+        <v>2</v>
       </c>
       <c r="X10">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="Y10">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="Z10" s="1" cm="1">
         <f t="array" ref="Z10">SUMPRODUCT((Tabelle1[Seite]=V10)*Tabelle1[Score_Gewichtet])</f>
-        <v>27.150000000000006</v>
+        <v>25.200000000000006</v>
       </c>
       <c r="AA10" s="1"/>
       <c r="AD10" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -2376,7 +2379,7 @@
       <c r="V11">
         <v>103</v>
       </c>
-      <c r="W11" s="3">
+      <c r="W11" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>101</v>
       </c>
@@ -2395,7 +2398,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -2443,7 +2446,7 @@
       <c r="V12">
         <v>111</v>
       </c>
-      <c r="W12" s="3">
+      <c r="W12" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>109</v>
       </c>
@@ -2462,7 +2465,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -2508,28 +2511,28 @@
         <v>87</v>
       </c>
       <c r="V13">
-        <v>4</v>
-      </c>
-      <c r="W13" s="3">
+        <v>114</v>
+      </c>
+      <c r="W13" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="X13">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="Y13">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z13" s="1" cm="1">
         <f t="array" ref="Z13">SUMPRODUCT((Tabelle1[Seite]=V13)*Tabelle1[Score_Gewichtet])</f>
-        <v>25.200000000000006</v>
+        <v>25.100000000000012</v>
       </c>
       <c r="AA13" s="1"/>
       <c r="AD13" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>11</v>
       </c>
@@ -2577,7 +2580,7 @@
       <c r="V14">
         <v>48</v>
       </c>
-      <c r="W14" s="3">
+      <c r="W14" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>46</v>
       </c>
@@ -2598,7 +2601,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>11</v>
       </c>
@@ -2644,28 +2647,28 @@
         <v>29</v>
       </c>
       <c r="V15">
-        <v>114</v>
-      </c>
-      <c r="W15" s="3">
+        <v>56</v>
+      </c>
+      <c r="W15" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
-        <v>112</v>
+        <v>54</v>
       </c>
       <c r="X15">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="Y15">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="Z15" s="1" cm="1">
         <f t="array" ref="Z15">SUMPRODUCT((Tabelle1[Seite]=V15)*Tabelle1[Score_Gewichtet])</f>
-        <v>25.100000000000012</v>
+        <v>25.050000000000004</v>
       </c>
       <c r="AA15" s="1"/>
       <c r="AD15" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>11</v>
       </c>
@@ -2711,25 +2714,31 @@
         <v>41</v>
       </c>
       <c r="V16">
-        <v>56</v>
-      </c>
-      <c r="W16" s="3">
+        <v>13</v>
+      </c>
+      <c r="W16" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="X16">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="Y16">
-        <v>80</v>
+        <v>8</v>
       </c>
       <c r="Z16" s="1" cm="1">
         <f t="array" ref="Z16">SUMPRODUCT((Tabelle1[Seite]=V16)*Tabelle1[Score_Gewichtet])</f>
-        <v>25.050000000000004</v>
-      </c>
-      <c r="AA16" s="1"/>
-      <c r="AD16" t="s">
+        <v>23.650000000000009</v>
+      </c>
+      <c r="AA16" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="AB16" t="s">
         <v>134</v>
+      </c>
+      <c r="AD16" t="str">
+        <f>IF(Tabelle3[[#This Row],[Summe Score]]&lt;5,"x","")</f>
+        <v/>
       </c>
     </row>
     <row r="17" spans="1:30" x14ac:dyDescent="0.2">
@@ -2778,31 +2787,25 @@
         <v>14</v>
       </c>
       <c r="V17">
-        <v>13</v>
-      </c>
-      <c r="W17" s="3">
+        <v>108</v>
+      </c>
+      <c r="W17" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
-        <v>11</v>
+        <v>106</v>
       </c>
       <c r="X17">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="Y17">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="Z17" s="1" cm="1">
         <f t="array" ref="Z17">SUMPRODUCT((Tabelle1[Seite]=V17)*Tabelle1[Score_Gewichtet])</f>
-        <v>23.650000000000009</v>
-      </c>
-      <c r="AA17" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="AB17" t="s">
+        <v>23.600000000000005</v>
+      </c>
+      <c r="AA17" s="1"/>
+      <c r="AD17" t="s">
         <v>134</v>
-      </c>
-      <c r="AD17" s="2" t="str">
-        <f>IF(Tabelle3[[#This Row],[Summe Score]]&lt;5,"x","")</f>
-        <v/>
       </c>
     </row>
     <row r="18" spans="1:30" x14ac:dyDescent="0.2">
@@ -2851,25 +2854,31 @@
         <v>47</v>
       </c>
       <c r="V18">
-        <v>108</v>
-      </c>
-      <c r="W18" s="3">
+        <v>98</v>
+      </c>
+      <c r="W18" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="X18">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Y18">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="Z18" s="1" cm="1">
         <f t="array" ref="Z18">SUMPRODUCT((Tabelle1[Seite]=V18)*Tabelle1[Score_Gewichtet])</f>
-        <v>23.600000000000005</v>
-      </c>
-      <c r="AA18" s="1"/>
-      <c r="AD18" t="s">
-        <v>134</v>
+        <v>22.20000000000001</v>
+      </c>
+      <c r="AA18" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>150</v>
+      </c>
+      <c r="AD18" t="str">
+        <f>IF(Tabelle3[[#This Row],[Summe Score]]&lt;5,"x","")</f>
+        <v/>
       </c>
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.2">
@@ -2920,7 +2929,7 @@
       <c r="V19">
         <v>80</v>
       </c>
-      <c r="W19" s="3">
+      <c r="W19" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>78</v>
       </c>
@@ -2988,7 +2997,7 @@
       <c r="V20">
         <v>82</v>
       </c>
-      <c r="W20" s="3">
+      <c r="W20" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>80</v>
       </c>
@@ -3060,7 +3069,7 @@
       <c r="V21">
         <v>104</v>
       </c>
-      <c r="W21" s="3">
+      <c r="W21" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>102</v>
       </c>
@@ -3125,31 +3134,25 @@
         <v>55</v>
       </c>
       <c r="V22">
-        <v>98</v>
-      </c>
-      <c r="W22" s="3">
+        <v>59</v>
+      </c>
+      <c r="W22" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
-        <v>96</v>
+        <v>57</v>
       </c>
       <c r="X22">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="Y22">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="Z22" s="1" cm="1">
         <f t="array" ref="Z22">SUMPRODUCT((Tabelle1[Seite]=V22)*Tabelle1[Score_Gewichtet])</f>
-        <v>22.20000000000001</v>
-      </c>
-      <c r="AA22" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="AB22" t="s">
-        <v>150</v>
-      </c>
-      <c r="AD22" t="str">
-        <f>IF(Tabelle3[[#This Row],[Summe Score]]&lt;5,"x","")</f>
-        <v/>
+        <v>21.650000000000002</v>
+      </c>
+      <c r="AA22" s="1"/>
+      <c r="AD22" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="23" spans="1:30" x14ac:dyDescent="0.2">
@@ -3200,7 +3203,7 @@
       <c r="V23">
         <v>17</v>
       </c>
-      <c r="W23" s="3">
+      <c r="W23" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>15</v>
       </c>
@@ -3265,21 +3268,21 @@
         <v>101</v>
       </c>
       <c r="V24">
-        <v>59</v>
-      </c>
-      <c r="W24" s="3">
+        <v>112</v>
+      </c>
+      <c r="W24" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
-        <v>57</v>
+        <v>110</v>
       </c>
       <c r="X24">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Y24">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="Z24" s="1" cm="1">
         <f t="array" ref="Z24">SUMPRODUCT((Tabelle1[Seite]=V24)*Tabelle1[Score_Gewichtet])</f>
-        <v>21.650000000000002</v>
+        <v>21.550000000000004</v>
       </c>
       <c r="AA24" s="1"/>
       <c r="AD24" t="s">
@@ -3332,21 +3335,21 @@
         <v>29</v>
       </c>
       <c r="V25">
-        <v>112</v>
-      </c>
-      <c r="W25" s="3">
+        <v>68</v>
+      </c>
+      <c r="W25" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
-        <v>110</v>
+        <v>66</v>
       </c>
       <c r="X25">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Y25">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="Z25" s="1" cm="1">
         <f t="array" ref="Z25">SUMPRODUCT((Tabelle1[Seite]=V25)*Tabelle1[Score_Gewichtet])</f>
-        <v>21.550000000000004</v>
+        <v>20.400000000000002</v>
       </c>
       <c r="AA25" s="1"/>
       <c r="AD25" t="s">
@@ -3401,7 +3404,7 @@
       <c r="V26">
         <v>83</v>
       </c>
-      <c r="W26" s="3">
+      <c r="W26" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>81</v>
       </c>
@@ -3468,7 +3471,7 @@
       <c r="V27">
         <v>51</v>
       </c>
-      <c r="W27" s="3">
+      <c r="W27" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>49</v>
       </c>
@@ -3535,7 +3538,7 @@
       <c r="V28">
         <v>44</v>
       </c>
-      <c r="W28" s="3">
+      <c r="W28" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>42</v>
       </c>
@@ -3555,7 +3558,6 @@
       <c r="AB28" t="s">
         <v>150</v>
       </c>
-      <c r="AD28" s="2"/>
     </row>
     <row r="29" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
@@ -3605,7 +3607,7 @@
       <c r="V29">
         <v>67</v>
       </c>
-      <c r="W29" s="3">
+      <c r="W29" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>65</v>
       </c>
@@ -3672,7 +3674,7 @@
       <c r="V30">
         <v>94</v>
       </c>
-      <c r="W30" s="3">
+      <c r="W30" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>92</v>
       </c>
@@ -3737,21 +3739,21 @@
         <v>65</v>
       </c>
       <c r="V31">
-        <v>68</v>
-      </c>
-      <c r="W31" s="3">
+        <v>65</v>
+      </c>
+      <c r="W31" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="X31">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="Y31">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="Z31" s="1" cm="1">
         <f t="array" ref="Z31">SUMPRODUCT((Tabelle1[Seite]=V31)*Tabelle1[Score_Gewichtet])</f>
-        <v>20.400000000000002</v>
+        <v>19.750000000000004</v>
       </c>
       <c r="AA31" s="1"/>
       <c r="AD31" t="s">
@@ -3806,7 +3808,7 @@
       <c r="V32">
         <v>9</v>
       </c>
-      <c r="W32" s="3">
+      <c r="W32" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>7</v>
       </c>
@@ -3871,21 +3873,21 @@
         <v>37</v>
       </c>
       <c r="V33">
-        <v>65</v>
-      </c>
-      <c r="W33" s="3">
+        <v>110</v>
+      </c>
+      <c r="W33" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
-        <v>63</v>
+        <v>108</v>
       </c>
       <c r="X33">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Y33">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="Z33" s="1" cm="1">
         <f t="array" ref="Z33">SUMPRODUCT((Tabelle1[Seite]=V33)*Tabelle1[Score_Gewichtet])</f>
-        <v>19.750000000000004</v>
+        <v>19.5</v>
       </c>
       <c r="AA33" s="1"/>
       <c r="AD33" t="s">
@@ -3938,25 +3940,31 @@
         <v>84</v>
       </c>
       <c r="V34">
-        <v>110</v>
-      </c>
-      <c r="W34" s="3">
+        <v>15</v>
+      </c>
+      <c r="W34" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
-        <v>108</v>
+        <v>13</v>
       </c>
       <c r="X34">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="Y34">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="Z34" s="1" cm="1">
         <f t="array" ref="Z34">SUMPRODUCT((Tabelle1[Seite]=V34)*Tabelle1[Score_Gewichtet])</f>
-        <v>19.5</v>
-      </c>
-      <c r="AA34" s="1"/>
-      <c r="AD34" t="s">
+        <v>18.7</v>
+      </c>
+      <c r="AA34" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="AB34" t="s">
         <v>134</v>
+      </c>
+      <c r="AD34" t="str">
+        <f>IF(Tabelle3[[#This Row],[Summe Score]]&lt;5,"x","")</f>
+        <v/>
       </c>
     </row>
     <row r="35" spans="1:30" x14ac:dyDescent="0.2">
@@ -4007,7 +4015,7 @@
       <c r="V35">
         <v>62</v>
       </c>
-      <c r="W35" s="3">
+      <c r="W35" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>60</v>
       </c>
@@ -4074,7 +4082,7 @@
       <c r="V36">
         <v>107</v>
       </c>
-      <c r="W36" s="3">
+      <c r="W36" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>105</v>
       </c>
@@ -4139,31 +4147,25 @@
         <v>55</v>
       </c>
       <c r="V37">
-        <v>15</v>
-      </c>
-      <c r="W37" s="3">
+        <v>106</v>
+      </c>
+      <c r="W37" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
-        <v>13</v>
+        <v>104</v>
       </c>
       <c r="X37">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="Y37">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="Z37" s="1" cm="1">
         <f t="array" ref="Z37">SUMPRODUCT((Tabelle1[Seite]=V37)*Tabelle1[Score_Gewichtet])</f>
-        <v>18.7</v>
-      </c>
-      <c r="AA37" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="AB37" t="s">
+        <v>18.350000000000009</v>
+      </c>
+      <c r="AA37" s="1"/>
+      <c r="AD37" t="s">
         <v>134</v>
-      </c>
-      <c r="AD37" t="str">
-        <f>IF(Tabelle3[[#This Row],[Summe Score]]&lt;5,"x","")</f>
-        <v/>
       </c>
     </row>
     <row r="38" spans="1:30" x14ac:dyDescent="0.2">
@@ -4214,7 +4216,7 @@
       <c r="V38">
         <v>90</v>
       </c>
-      <c r="W38" s="3">
+      <c r="W38" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>88</v>
       </c>
@@ -4285,23 +4287,25 @@
         <v>94</v>
       </c>
       <c r="V39">
-        <v>106</v>
-      </c>
-      <c r="W39" s="3">
+        <v>102</v>
+      </c>
+      <c r="W39" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="X39">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="Y39">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="Z39" s="1" cm="1">
         <f t="array" ref="Z39">SUMPRODUCT((Tabelle1[Seite]=V39)*Tabelle1[Score_Gewichtet])</f>
-        <v>18.350000000000009</v>
-      </c>
-      <c r="AA39" s="1"/>
+        <v>17.850000000000005</v>
+      </c>
+      <c r="AA39" s="1" t="s">
+        <v>162</v>
+      </c>
       <c r="AD39" t="s">
         <v>134</v>
       </c>
@@ -4354,7 +4358,7 @@
       <c r="V40">
         <v>10</v>
       </c>
-      <c r="W40" s="3">
+      <c r="W40" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>8</v>
       </c>
@@ -4369,7 +4373,7 @@
         <v>17.950000000000003</v>
       </c>
       <c r="AA40" s="1"/>
-      <c r="AD40" s="2" t="s">
+      <c r="AD40" t="s">
         <v>134</v>
       </c>
     </row>
@@ -4419,25 +4423,23 @@
         <v>24</v>
       </c>
       <c r="V41">
-        <v>102</v>
-      </c>
-      <c r="W41" s="3">
+        <v>87</v>
+      </c>
+      <c r="W41" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="X41">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="Y41">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="Z41" s="1" cm="1">
         <f t="array" ref="Z41">SUMPRODUCT((Tabelle1[Seite]=V41)*Tabelle1[Score_Gewichtet])</f>
-        <v>17.850000000000005</v>
-      </c>
-      <c r="AA41" s="1" t="s">
-        <v>162</v>
-      </c>
+        <v>17.700000000000003</v>
+      </c>
+      <c r="AA41" s="1"/>
       <c r="AD41" t="s">
         <v>134</v>
       </c>
@@ -4490,7 +4492,7 @@
       <c r="V42">
         <v>55</v>
       </c>
-      <c r="W42" s="3">
+      <c r="W42" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>53</v>
       </c>
@@ -4555,21 +4557,21 @@
         <v>4</v>
       </c>
       <c r="V43">
-        <v>87</v>
-      </c>
-      <c r="W43" s="3">
+        <v>97</v>
+      </c>
+      <c r="W43" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="X43">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="Y43">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="Z43" s="1" cm="1">
         <f t="array" ref="Z43">SUMPRODUCT((Tabelle1[Seite]=V43)*Tabelle1[Score_Gewichtet])</f>
-        <v>17.700000000000003</v>
+        <v>17.500000000000007</v>
       </c>
       <c r="AA43" s="1"/>
       <c r="AD43" t="s">
@@ -4622,21 +4624,21 @@
         <v>108</v>
       </c>
       <c r="V44">
-        <v>97</v>
-      </c>
-      <c r="W44" s="3">
+        <v>8</v>
+      </c>
+      <c r="W44" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
-        <v>95</v>
+        <v>6</v>
       </c>
       <c r="X44">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Y44">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Z44" s="1" cm="1">
         <f t="array" ref="Z44">SUMPRODUCT((Tabelle1[Seite]=V44)*Tabelle1[Score_Gewichtet])</f>
-        <v>17.500000000000007</v>
+        <v>17.500000000000004</v>
       </c>
       <c r="AA44" s="1"/>
       <c r="AD44" t="s">
@@ -4689,21 +4691,21 @@
         <v>94</v>
       </c>
       <c r="V45">
-        <v>8</v>
-      </c>
-      <c r="W45" s="3">
+        <v>5</v>
+      </c>
+      <c r="W45" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="X45">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="Y45">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="Z45" s="1" cm="1">
         <f t="array" ref="Z45">SUMPRODUCT((Tabelle1[Seite]=V45)*Tabelle1[Score_Gewichtet])</f>
-        <v>17.500000000000004</v>
+        <v>16.850000000000001</v>
       </c>
       <c r="AA45" s="1"/>
       <c r="AD45" t="s">
@@ -4756,21 +4758,21 @@
         <v>47</v>
       </c>
       <c r="V46">
-        <v>5</v>
-      </c>
-      <c r="W46" s="3">
+        <v>66</v>
+      </c>
+      <c r="W46" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="X46">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="Y46">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="Z46" s="1" cm="1">
         <f t="array" ref="Z46">SUMPRODUCT((Tabelle1[Seite]=V46)*Tabelle1[Score_Gewichtet])</f>
-        <v>16.850000000000001</v>
+        <v>15.499999999999998</v>
       </c>
       <c r="AA46" s="1"/>
       <c r="AD46" t="s">
@@ -4825,7 +4827,7 @@
       <c r="V47">
         <v>33</v>
       </c>
-      <c r="W47" s="3">
+      <c r="W47" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>31</v>
       </c>
@@ -4892,7 +4894,7 @@
       <c r="V48">
         <v>23</v>
       </c>
-      <c r="W48" s="3">
+      <c r="W48" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>21</v>
       </c>
@@ -4907,7 +4909,7 @@
         <v>16.500000000000004</v>
       </c>
       <c r="AA48" s="1"/>
-      <c r="AD48" s="2" t="s">
+      <c r="AD48" t="s">
         <v>134</v>
       </c>
     </row>
@@ -4959,7 +4961,7 @@
       <c r="V49">
         <v>57</v>
       </c>
-      <c r="W49" s="3">
+      <c r="W49" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>55</v>
       </c>
@@ -5032,7 +5034,7 @@
       <c r="V50">
         <v>100</v>
       </c>
-      <c r="W50" s="3">
+      <c r="W50" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>98</v>
       </c>
@@ -5099,21 +5101,21 @@
         <v>65</v>
       </c>
       <c r="V51">
-        <v>66</v>
-      </c>
-      <c r="W51" s="3">
+        <v>34</v>
+      </c>
+      <c r="W51" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="X51">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Y51">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="Z51" s="1" cm="1">
         <f t="array" ref="Z51">SUMPRODUCT((Tabelle1[Seite]=V51)*Tabelle1[Score_Gewichtet])</f>
-        <v>15.499999999999998</v>
+        <v>15</v>
       </c>
       <c r="AA51" s="1"/>
       <c r="AD51" t="s">
@@ -5168,7 +5170,7 @@
       <c r="V52">
         <v>96</v>
       </c>
-      <c r="W52" s="3">
+      <c r="W52" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>94</v>
       </c>
@@ -5241,7 +5243,7 @@
       <c r="V53">
         <v>64</v>
       </c>
-      <c r="W53" s="3">
+      <c r="W53" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>62</v>
       </c>
@@ -5306,21 +5308,21 @@
         <v>73</v>
       </c>
       <c r="V54">
-        <v>34</v>
-      </c>
-      <c r="W54" s="3">
+        <v>22</v>
+      </c>
+      <c r="W54" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="X54">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="Y54">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="Z54" s="1" cm="1">
         <f t="array" ref="Z54">SUMPRODUCT((Tabelle1[Seite]=V54)*Tabelle1[Score_Gewichtet])</f>
-        <v>15</v>
+        <v>14.95</v>
       </c>
       <c r="AA54" s="1"/>
       <c r="AD54" t="s">
@@ -5373,25 +5375,31 @@
         <v>80</v>
       </c>
       <c r="V55">
-        <v>22</v>
-      </c>
-      <c r="W55" s="3">
+        <v>74</v>
+      </c>
+      <c r="W55" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="X55">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="Y55">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="Z55" s="1" cm="1">
         <f t="array" ref="Z55">SUMPRODUCT((Tabelle1[Seite]=V55)*Tabelle1[Score_Gewichtet])</f>
-        <v>14.95</v>
-      </c>
-      <c r="AA55" s="1"/>
-      <c r="AD55" s="2" t="s">
-        <v>134</v>
+        <v>14.499999999999996</v>
+      </c>
+      <c r="AA55" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="AB55" t="s">
+        <v>150</v>
+      </c>
+      <c r="AD55" t="str">
+        <f>IF(Tabelle3[[#This Row],[Summe Score]]&lt;5,"x","")</f>
+        <v/>
       </c>
     </row>
     <row r="56" spans="1:30" x14ac:dyDescent="0.2">
@@ -5442,7 +5450,7 @@
       <c r="V56">
         <v>105</v>
       </c>
-      <c r="W56" s="3">
+      <c r="W56" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>103</v>
       </c>
@@ -5509,7 +5517,7 @@
       <c r="V57">
         <v>86</v>
       </c>
-      <c r="W57" s="3">
+      <c r="W57" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>84</v>
       </c>
@@ -5574,31 +5582,25 @@
         <v>47</v>
       </c>
       <c r="V58">
-        <v>74</v>
-      </c>
-      <c r="W58" s="3">
+        <v>19</v>
+      </c>
+      <c r="W58" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
-        <v>72</v>
+        <v>17</v>
       </c>
       <c r="X58">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="Y58">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="Z58" s="1" cm="1">
         <f t="array" ref="Z58">SUMPRODUCT((Tabelle1[Seite]=V58)*Tabelle1[Score_Gewichtet])</f>
-        <v>14.499999999999996</v>
-      </c>
-      <c r="AA58" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="AB58" t="s">
-        <v>150</v>
-      </c>
-      <c r="AD58" t="str">
-        <f>IF(Tabelle3[[#This Row],[Summe Score]]&lt;5,"x","")</f>
-        <v/>
+        <v>14.45</v>
+      </c>
+      <c r="AA58" s="1"/>
+      <c r="AD58" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="59" spans="1:30" x14ac:dyDescent="0.2">
@@ -5647,25 +5649,31 @@
         <v>47</v>
       </c>
       <c r="V59">
+        <v>24</v>
+      </c>
+      <c r="W59" s="2">
+        <f>Tabelle3[[#This Row],[Seite]]-2</f>
+        <v>22</v>
+      </c>
+      <c r="X59">
         <v>19</v>
       </c>
-      <c r="W59" s="3">
-        <f>Tabelle3[[#This Row],[Seite]]-2</f>
-        <v>17</v>
-      </c>
-      <c r="X59">
-        <v>14</v>
-      </c>
       <c r="Y59">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="Z59" s="1" cm="1">
         <f t="array" ref="Z59">SUMPRODUCT((Tabelle1[Seite]=V59)*Tabelle1[Score_Gewichtet])</f>
-        <v>14.45</v>
-      </c>
-      <c r="AA59" s="1"/>
-      <c r="AD59" t="s">
+        <v>13.799999999999995</v>
+      </c>
+      <c r="AA59" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="AB59" t="s">
         <v>134</v>
+      </c>
+      <c r="AD59" t="str">
+        <f>IF(Tabelle3[[#This Row],[Summe Score]]&lt;5,"x","")</f>
+        <v/>
       </c>
     </row>
     <row r="60" spans="1:30" x14ac:dyDescent="0.2">
@@ -5716,7 +5724,7 @@
       <c r="V60">
         <v>49</v>
       </c>
-      <c r="W60" s="3">
+      <c r="W60" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>47</v>
       </c>
@@ -5783,31 +5791,25 @@
         <v>24</v>
       </c>
       <c r="V61">
-        <v>24</v>
-      </c>
-      <c r="W61" s="3">
+        <v>18</v>
+      </c>
+      <c r="W61" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="X61">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Y61">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="Z61" s="1" cm="1">
         <f t="array" ref="Z61">SUMPRODUCT((Tabelle1[Seite]=V61)*Tabelle1[Score_Gewichtet])</f>
-        <v>13.799999999999995</v>
-      </c>
-      <c r="AA61" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="AB61" t="s">
+        <v>13.049999999999999</v>
+      </c>
+      <c r="AA61" s="1"/>
+      <c r="AD61" t="s">
         <v>134</v>
-      </c>
-      <c r="AD61" t="str">
-        <f>IF(Tabelle3[[#This Row],[Summe Score]]&lt;5,"x","")</f>
-        <v/>
       </c>
     </row>
     <row r="62" spans="1:30" x14ac:dyDescent="0.2">
@@ -5858,7 +5860,7 @@
       <c r="V62">
         <v>36</v>
       </c>
-      <c r="W62" s="3">
+      <c r="W62" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>34</v>
       </c>
@@ -5923,21 +5925,21 @@
         <v>73</v>
       </c>
       <c r="V63">
+        <v>42</v>
+      </c>
+      <c r="W63" s="2">
+        <f>Tabelle3[[#This Row],[Seite]]-2</f>
+        <v>40</v>
+      </c>
+      <c r="X63">
         <v>18</v>
       </c>
-      <c r="W63" s="3">
-        <f>Tabelle3[[#This Row],[Seite]]-2</f>
-        <v>16</v>
-      </c>
-      <c r="X63">
-        <v>20</v>
-      </c>
       <c r="Y63">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="Z63" s="1" cm="1">
         <f t="array" ref="Z63">SUMPRODUCT((Tabelle1[Seite]=V63)*Tabelle1[Score_Gewichtet])</f>
-        <v>13.049999999999999</v>
+        <v>11.85</v>
       </c>
       <c r="AA63" s="1"/>
       <c r="AD63" t="s">
@@ -5992,7 +5994,7 @@
       <c r="V64">
         <v>91</v>
       </c>
-      <c r="W64" s="3">
+      <c r="W64" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>89</v>
       </c>
@@ -6061,7 +6063,7 @@
       <c r="V65">
         <v>58</v>
       </c>
-      <c r="W65" s="3">
+      <c r="W65" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>56</v>
       </c>
@@ -6134,7 +6136,7 @@
       <c r="V66">
         <v>95</v>
       </c>
-      <c r="W66" s="3">
+      <c r="W66" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>93</v>
       </c>
@@ -6201,7 +6203,7 @@
       <c r="V67">
         <v>11</v>
       </c>
-      <c r="W67" s="3">
+      <c r="W67" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>9</v>
       </c>
@@ -6216,7 +6218,7 @@
         <v>12.349999999999998</v>
       </c>
       <c r="AA67" s="1"/>
-      <c r="AD67" s="2" t="s">
+      <c r="AD67" t="s">
         <v>134</v>
       </c>
     </row>
@@ -6268,7 +6270,7 @@
       <c r="V68">
         <v>38</v>
       </c>
-      <c r="W68" s="3">
+      <c r="W68" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>36</v>
       </c>
@@ -6333,24 +6335,24 @@
         <v>55</v>
       </c>
       <c r="V69">
-        <v>42</v>
-      </c>
-      <c r="W69" s="3">
+        <v>26</v>
+      </c>
+      <c r="W69" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="X69">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y69">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="Z69" s="1" cm="1">
         <f t="array" ref="Z69">SUMPRODUCT((Tabelle1[Seite]=V69)*Tabelle1[Score_Gewichtet])</f>
-        <v>11.85</v>
+        <v>11.649999999999999</v>
       </c>
       <c r="AA69" s="1"/>
-      <c r="AD69" s="2" t="s">
+      <c r="AD69" t="s">
         <v>134</v>
       </c>
     </row>
@@ -6402,7 +6404,7 @@
       <c r="V70">
         <v>60</v>
       </c>
-      <c r="W70" s="3">
+      <c r="W70" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>58</v>
       </c>
@@ -6467,24 +6469,26 @@
         <v>87</v>
       </c>
       <c r="V71">
-        <v>26</v>
-      </c>
-      <c r="W71" s="3">
+        <v>71</v>
+      </c>
+      <c r="W71" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="X71">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Y71">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="Z71" s="1" cm="1">
         <f t="array" ref="Z71">SUMPRODUCT((Tabelle1[Seite]=V71)*Tabelle1[Score_Gewichtet])</f>
-        <v>11.649999999999999</v>
-      </c>
-      <c r="AA71" s="1"/>
-      <c r="AD71" t="s">
+        <v>11.55</v>
+      </c>
+      <c r="AA71" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="AB71" t="s">
         <v>134</v>
       </c>
     </row>
@@ -6534,26 +6538,24 @@
         <v>73</v>
       </c>
       <c r="V72">
-        <v>71</v>
-      </c>
-      <c r="W72" s="3">
+        <v>52</v>
+      </c>
+      <c r="W72" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="X72">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y72">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="Z72" s="1" cm="1">
         <f t="array" ref="Z72">SUMPRODUCT((Tabelle1[Seite]=V72)*Tabelle1[Score_Gewichtet])</f>
-        <v>11.55</v>
-      </c>
-      <c r="AA72" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="AB72" t="s">
+        <v>10.899999999999997</v>
+      </c>
+      <c r="AA72" s="1"/>
+      <c r="AD72" t="s">
         <v>134</v>
       </c>
     </row>
@@ -6605,7 +6607,7 @@
       <c r="V73">
         <v>32</v>
       </c>
-      <c r="W73" s="3">
+      <c r="W73" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>30</v>
       </c>
@@ -6672,7 +6674,7 @@
       <c r="V74">
         <v>20</v>
       </c>
-      <c r="W74" s="3">
+      <c r="W74" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>18</v>
       </c>
@@ -6737,21 +6739,21 @@
         <v>14</v>
       </c>
       <c r="V75">
-        <v>52</v>
-      </c>
-      <c r="W75" s="3">
+        <v>41</v>
+      </c>
+      <c r="W75" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="X75">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Y75">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="Z75" s="1" cm="1">
         <f t="array" ref="Z75">SUMPRODUCT((Tabelle1[Seite]=V75)*Tabelle1[Score_Gewichtet])</f>
-        <v>10.899999999999997</v>
+        <v>10.7</v>
       </c>
       <c r="AA75" s="1"/>
       <c r="AD75" t="s">
@@ -6804,25 +6806,27 @@
         <v>80</v>
       </c>
       <c r="V76">
-        <v>41</v>
-      </c>
-      <c r="W76" s="3">
+        <v>101</v>
+      </c>
+      <c r="W76" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="X76">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="Y76">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="Z76" s="1" cm="1">
         <f t="array" ref="Z76">SUMPRODUCT((Tabelle1[Seite]=V76)*Tabelle1[Score_Gewichtet])</f>
-        <v>10.7</v>
-      </c>
-      <c r="AA76" s="1"/>
-      <c r="AD76" t="s">
-        <v>134</v>
+        <v>10.599999999999996</v>
+      </c>
+      <c r="AA76" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="AB76" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="77" spans="1:30" x14ac:dyDescent="0.2">
@@ -6873,7 +6877,7 @@
       <c r="V77">
         <v>76</v>
       </c>
-      <c r="W77" s="3">
+      <c r="W77" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>74</v>
       </c>
@@ -6938,27 +6942,25 @@
         <v>41</v>
       </c>
       <c r="V78">
-        <v>101</v>
-      </c>
-      <c r="W78" s="3">
+        <v>75</v>
+      </c>
+      <c r="W78" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
-        <v>99</v>
+        <v>73</v>
       </c>
       <c r="X78">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="Y78">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="Z78" s="1" cm="1">
         <f t="array" ref="Z78">SUMPRODUCT((Tabelle1[Seite]=V78)*Tabelle1[Score_Gewichtet])</f>
-        <v>10.599999999999996</v>
-      </c>
-      <c r="AA78" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="AB78" t="s">
-        <v>150</v>
+        <v>10.199999999999999</v>
+      </c>
+      <c r="AA78" s="1"/>
+      <c r="AD78" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="79" spans="1:30" x14ac:dyDescent="0.2">
@@ -7009,7 +7011,7 @@
       <c r="V79">
         <v>63</v>
       </c>
-      <c r="W79" s="3">
+      <c r="W79" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>61</v>
       </c>
@@ -7074,25 +7076,31 @@
         <v>94</v>
       </c>
       <c r="V80">
-        <v>75</v>
-      </c>
-      <c r="W80" s="3">
+        <v>14</v>
+      </c>
+      <c r="W80" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
-        <v>73</v>
+        <v>12</v>
       </c>
       <c r="X80">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="Y80">
-        <v>41</v>
+        <v>88</v>
       </c>
       <c r="Z80" s="1" cm="1">
         <f t="array" ref="Z80">SUMPRODUCT((Tabelle1[Seite]=V80)*Tabelle1[Score_Gewichtet])</f>
-        <v>10.199999999999999</v>
-      </c>
-      <c r="AA80" s="1"/>
-      <c r="AD80" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA80" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="AB80" t="s">
         <v>134</v>
+      </c>
+      <c r="AD80" t="str">
+        <f>IF(Tabelle3[[#This Row],[Summe Score]]&lt;5,"x","")</f>
+        <v/>
       </c>
     </row>
     <row r="81" spans="1:30" x14ac:dyDescent="0.2">
@@ -7141,31 +7149,25 @@
         <v>37</v>
       </c>
       <c r="V81">
-        <v>14</v>
-      </c>
-      <c r="W81" s="3">
+        <v>43</v>
+      </c>
+      <c r="W81" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
+        <v>41</v>
+      </c>
+      <c r="X81">
         <v>12</v>
       </c>
-      <c r="X81">
-        <v>8</v>
-      </c>
       <c r="Y81">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="Z81" s="1" cm="1">
         <f t="array" ref="Z81">SUMPRODUCT((Tabelle1[Seite]=V81)*Tabelle1[Score_Gewichtet])</f>
-        <v>10</v>
-      </c>
-      <c r="AA81" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="AB81" t="s">
+        <v>9.0499999999999989</v>
+      </c>
+      <c r="AA81" s="1"/>
+      <c r="AD81" t="s">
         <v>134</v>
-      </c>
-      <c r="AD81" t="str">
-        <f>IF(Tabelle3[[#This Row],[Summe Score]]&lt;5,"x","")</f>
-        <v/>
       </c>
     </row>
     <row r="82" spans="1:30" x14ac:dyDescent="0.2">
@@ -7216,7 +7218,7 @@
       <c r="V82">
         <v>54</v>
       </c>
-      <c r="W82" s="3">
+      <c r="W82" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>52</v>
       </c>
@@ -7283,7 +7285,7 @@
       <c r="V83">
         <v>92</v>
       </c>
-      <c r="W83" s="3">
+      <c r="W83" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>90</v>
       </c>
@@ -7348,24 +7350,24 @@
         <v>84</v>
       </c>
       <c r="V84">
-        <v>43</v>
-      </c>
-      <c r="W84" s="3">
+        <v>27</v>
+      </c>
+      <c r="W84" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="X84">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y84">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="Z84" s="1" cm="1">
         <f t="array" ref="Z84">SUMPRODUCT((Tabelle1[Seite]=V84)*Tabelle1[Score_Gewichtet])</f>
-        <v>9.0499999999999989</v>
+        <v>8.1</v>
       </c>
       <c r="AA84" s="1"/>
-      <c r="AD84" s="2" t="s">
+      <c r="AD84" t="s">
         <v>134</v>
       </c>
     </row>
@@ -7417,7 +7419,7 @@
       <c r="V85">
         <v>84</v>
       </c>
-      <c r="W85" s="3">
+      <c r="W85" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>82</v>
       </c>
@@ -7484,7 +7486,7 @@
       <c r="V86">
         <v>72</v>
       </c>
-      <c r="W86" s="3">
+      <c r="W86" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>70</v>
       </c>
@@ -7555,21 +7557,21 @@
         <v>2</v>
       </c>
       <c r="V87">
-        <v>27</v>
-      </c>
-      <c r="W87" s="3">
+        <v>35</v>
+      </c>
+      <c r="W87" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="X87">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Y87">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="Z87" s="1" cm="1">
         <f t="array" ref="Z87">SUMPRODUCT((Tabelle1[Seite]=V87)*Tabelle1[Score_Gewichtet])</f>
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
       <c r="AA87" s="1"/>
       <c r="AD87" t="s">
@@ -7624,7 +7626,7 @@
       <c r="V88">
         <v>73</v>
       </c>
-      <c r="W88" s="3">
+      <c r="W88" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>71</v>
       </c>
@@ -7695,21 +7697,21 @@
         <v>41</v>
       </c>
       <c r="V89">
-        <v>35</v>
-      </c>
-      <c r="W89" s="3">
+        <v>29</v>
+      </c>
+      <c r="W89" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="X89">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y89">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="Z89" s="1" cm="1">
         <f t="array" ref="Z89">SUMPRODUCT((Tabelle1[Seite]=V89)*Tabelle1[Score_Gewichtet])</f>
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="AA89" s="1"/>
       <c r="AD89" t="s">
@@ -7764,7 +7766,7 @@
       <c r="V90">
         <v>116</v>
       </c>
-      <c r="W90" s="3">
+      <c r="W90" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>114</v>
       </c>
@@ -7831,7 +7833,7 @@
       <c r="V91">
         <v>12</v>
       </c>
-      <c r="W91" s="3">
+      <c r="W91" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>10</v>
       </c>
@@ -7846,7 +7848,7 @@
         <v>7.4499999999999993</v>
       </c>
       <c r="AA91" s="1"/>
-      <c r="AD91" s="2" t="s">
+      <c r="AD91" t="s">
         <v>134</v>
       </c>
     </row>
@@ -7896,21 +7898,21 @@
         <v>110</v>
       </c>
       <c r="V92">
-        <v>29</v>
-      </c>
-      <c r="W92" s="3">
+        <v>70</v>
+      </c>
+      <c r="W92" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="X92">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Y92">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="Z92" s="1" cm="1">
         <f t="array" ref="Z92">SUMPRODUCT((Tabelle1[Seite]=V92)*Tabelle1[Score_Gewichtet])</f>
-        <v>7.3</v>
+        <v>5.049999999999998</v>
       </c>
       <c r="AA92" s="1"/>
       <c r="AD92" t="s">
@@ -7965,7 +7967,7 @@
       <c r="V93">
         <v>85</v>
       </c>
-      <c r="W93" s="3">
+      <c r="W93" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>83</v>
       </c>
@@ -8032,7 +8034,7 @@
       <c r="V94">
         <v>81</v>
       </c>
-      <c r="W94" s="3">
+      <c r="W94" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>79</v>
       </c>
@@ -8099,7 +8101,7 @@
       <c r="V95">
         <v>7</v>
       </c>
-      <c r="W95" s="3">
+      <c r="W95" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>5</v>
       </c>
@@ -8166,7 +8168,7 @@
       <c r="V96">
         <v>77</v>
       </c>
-      <c r="W96" s="3">
+      <c r="W96" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>75</v>
       </c>
@@ -8233,7 +8235,7 @@
       <c r="V97">
         <v>25</v>
       </c>
-      <c r="W97" s="3">
+      <c r="W97" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>23</v>
       </c>
@@ -8306,7 +8308,7 @@
       <c r="V98">
         <v>40</v>
       </c>
-      <c r="W98" s="3">
+      <c r="W98" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>38</v>
       </c>
@@ -8373,7 +8375,7 @@
       <c r="V99">
         <v>78</v>
       </c>
-      <c r="W99" s="3">
+      <c r="W99" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>76</v>
       </c>
@@ -8440,7 +8442,7 @@
       <c r="V100">
         <v>61</v>
       </c>
-      <c r="W100" s="3">
+      <c r="W100" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>59</v>
       </c>
@@ -8507,7 +8509,7 @@
       <c r="V101">
         <v>50</v>
       </c>
-      <c r="W101" s="3">
+      <c r="W101" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>48</v>
       </c>
@@ -8574,7 +8576,7 @@
       <c r="V102">
         <v>28</v>
       </c>
-      <c r="W102" s="3">
+      <c r="W102" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>26</v>
       </c>
@@ -8641,7 +8643,7 @@
       <c r="V103">
         <v>39</v>
       </c>
-      <c r="W103" s="3">
+      <c r="W103" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>37</v>
       </c>
@@ -8706,24 +8708,26 @@
         <v>55</v>
       </c>
       <c r="V104">
-        <v>70</v>
-      </c>
-      <c r="W104" s="3">
+        <v>46</v>
+      </c>
+      <c r="W104" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="X104">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="Y104">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="Z104" s="1" cm="1">
         <f t="array" ref="Z104">SUMPRODUCT((Tabelle1[Seite]=V104)*Tabelle1[Score_Gewichtet])</f>
-        <v>5.049999999999998</v>
-      </c>
-      <c r="AA104" s="1"/>
-      <c r="AD104" t="s">
+        <v>4.6999999999999993</v>
+      </c>
+      <c r="AA104" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="AB104" t="s">
         <v>134</v>
       </c>
     </row>
@@ -8775,7 +8779,7 @@
       <c r="V105">
         <v>53</v>
       </c>
-      <c r="W105" s="3">
+      <c r="W105" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>51</v>
       </c>
@@ -8840,29 +8844,26 @@
         <v>14</v>
       </c>
       <c r="V106">
-        <v>46</v>
-      </c>
-      <c r="W106" s="3">
+        <v>37</v>
+      </c>
+      <c r="W106" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="X106">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y106">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="Z106" s="1" cm="1">
         <f t="array" ref="Z106">SUMPRODUCT((Tabelle1[Seite]=V106)*Tabelle1[Score_Gewichtet])</f>
-        <v>4.6999999999999993</v>
-      </c>
-      <c r="AA106" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="AB106" t="s">
+        <v>4.1499999999999995</v>
+      </c>
+      <c r="AA106" s="1"/>
+      <c r="AD106" t="s">
         <v>134</v>
       </c>
-      <c r="AD106" s="2"/>
     </row>
     <row r="107" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
@@ -8910,21 +8911,21 @@
         <v>29</v>
       </c>
       <c r="V107">
-        <v>37</v>
-      </c>
-      <c r="W107" s="3">
+        <v>99</v>
+      </c>
+      <c r="W107" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
-        <v>35</v>
+        <v>97</v>
       </c>
       <c r="X107">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y107">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="Z107" s="1" cm="1">
         <f t="array" ref="Z107">SUMPRODUCT((Tabelle1[Seite]=V107)*Tabelle1[Score_Gewichtet])</f>
-        <v>4.1499999999999995</v>
+        <v>4.05</v>
       </c>
       <c r="AA107" s="1"/>
       <c r="AD107" t="s">
@@ -8977,25 +8978,26 @@
         <v>73</v>
       </c>
       <c r="V108">
-        <v>99</v>
-      </c>
-      <c r="W108" s="3">
+        <v>1</v>
+      </c>
+      <c r="W108" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
-        <v>97</v>
+        <v>-1</v>
       </c>
       <c r="X108">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y108">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="Z108" s="1" cm="1">
         <f t="array" ref="Z108">SUMPRODUCT((Tabelle1[Seite]=V108)*Tabelle1[Score_Gewichtet])</f>
-        <v>4.05</v>
+        <v>0.1</v>
       </c>
       <c r="AA108" s="1"/>
-      <c r="AD108" t="s">
-        <v>134</v>
+      <c r="AD108" t="str">
+        <f>IF(Tabelle3[[#This Row],[Summe Score]]&lt;5,"x","")</f>
+        <v>x</v>
       </c>
     </row>
     <row r="109" spans="1:30" x14ac:dyDescent="0.2">
@@ -9046,7 +9048,7 @@
       <c r="V109">
         <v>69</v>
       </c>
-      <c r="W109" s="3">
+      <c r="W109" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>67</v>
       </c>
@@ -9114,7 +9116,7 @@
       <c r="V110">
         <v>21</v>
       </c>
-      <c r="W110" s="3">
+      <c r="W110" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>19</v>
       </c>
@@ -9182,7 +9184,7 @@
       <c r="V111">
         <v>93</v>
       </c>
-      <c r="W111" s="3">
+      <c r="W111" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>91</v>
       </c>
@@ -9250,7 +9252,7 @@
       <c r="V112">
         <v>3</v>
       </c>
-      <c r="W112" s="3">
+      <c r="W112" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>1</v>
       </c>
@@ -9270,7 +9272,7 @@
         <v>x</v>
       </c>
     </row>
-    <row r="113" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>11</v>
       </c>
@@ -9318,7 +9320,7 @@
       <c r="V113">
         <v>45</v>
       </c>
-      <c r="W113" s="3">
+      <c r="W113" s="2">
         <f>Tabelle3[[#This Row],[Seite]]-2</f>
         <v>43</v>
       </c>
@@ -9338,9 +9340,8 @@
       <c r="AB113" t="s">
         <v>150</v>
       </c>
-      <c r="AD113" s="2"/>
-    </row>
-    <row r="114" spans="1:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="114" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>11</v>
       </c>
@@ -9375,7 +9376,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="115" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>11</v>
       </c>
@@ -9414,7 +9415,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="116" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>11</v>
       </c>
@@ -9449,7 +9450,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>11</v>
       </c>
@@ -9484,7 +9485,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="118" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>11</v>
       </c>
@@ -9519,7 +9520,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="119" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>11</v>
       </c>
@@ -9554,7 +9555,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="120" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>11</v>
       </c>
@@ -9589,7 +9590,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="121" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>11</v>
       </c>
@@ -9624,7 +9625,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="122" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>11</v>
       </c>
@@ -9659,7 +9660,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="123" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>11</v>
       </c>
@@ -9694,7 +9695,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="124" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>11</v>
       </c>
@@ -9729,7 +9730,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="125" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>11</v>
       </c>
@@ -9764,7 +9765,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="126" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>11</v>
       </c>
@@ -9799,7 +9800,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="127" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>11</v>
       </c>
@@ -9834,7 +9835,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="128" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>11</v>
       </c>

--- a/25-11-pdf-Analyzer/analyse_ergebnisse_v4-Mathbuch1.xlsx
+++ b/25-11-pdf-Analyzer/analyse_ergebnisse_v4-Mathbuch1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/131a8beddc4e0454/01JupyterAndCo/04GitHub/GitHubCloneMac/richard4231.github.io/25-11-pdf-Analyzer/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/131a8beddc4e0454/01JupyterAndCo/04GitHub/GitHubCloneMBP/richard4231.github.io/25-11-pdf-Analyzer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="349" documentId="8_{520C6DA0-CDB0-624A-9949-4D5B6898A185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B95C6D3-2903-574F-BFB6-89699A7B38D5}"/>
+  <xr:revisionPtr revIDLastSave="356" documentId="8_{520C6DA0-CDB0-624A-9949-4D5B6898A185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07ED0D91-A0C6-D445-869C-2564EB5D5513}"/>
   <bookViews>
-    <workbookView xWindow="17720" yWindow="5680" windowWidth="26040" windowHeight="15240" xr2:uid="{F946418D-52D0-4E49-9A8C-9784AA1B6916}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="27040" windowHeight="16960" xr2:uid="{F946418D-52D0-4E49-9A8C-9784AA1B6916}"/>
   </bookViews>
   <sheets>
     <sheet name="analyse_ergebnisse_v4-Mathbuch1" sheetId="1" r:id="rId1"/>
@@ -1109,10 +1109,10 @@
   </cellStyles>
   <dxfs count="4">
     <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <numFmt numFmtId="164" formatCode="0.0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="0.0"/>
@@ -1293,13 +1293,13 @@
     </tableColumn>
     <tableColumn id="2" xr3:uid="{B8F867EA-5D14-7E4C-8895-3EA33DED557A}" name="Anzahl"/>
     <tableColumn id="3" xr3:uid="{AA9B75F7-387B-2C4D-9051-47B9A42EC4A5}" name="Rang"/>
-    <tableColumn id="4" xr3:uid="{684ACF35-1508-3E48-8C5A-9F196266158C}" name="Summe Score" dataDxfId="0">
+    <tableColumn id="4" xr3:uid="{684ACF35-1508-3E48-8C5A-9F196266158C}" name="Summe Score" dataDxfId="2">
       <calculatedColumnFormula array="1">SUMPRODUCT((Tabelle1[Seite]=V2)*Tabelle1[Score_Gewichtet])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{4C63FC84-FA0F-B746-B1EA-28FD761487ED}" name="Thema" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{4C63FC84-FA0F-B746-B1EA-28FD761487ED}" name="Thema" dataDxfId="1"/>
     <tableColumn id="5" xr3:uid="{7A9789D8-EE21-4F46-878E-F11CD8F07DB7}" name="implizit"/>
     <tableColumn id="6" xr3:uid="{F78D389C-6566-B34B-A4EE-4303445DEBC7}" name="explizit"/>
-    <tableColumn id="8" xr3:uid="{9066A753-44BD-564B-BEB0-F50B4A150FF0}" name="ohne BNE-Bezug" dataDxfId="1">
+    <tableColumn id="8" xr3:uid="{9066A753-44BD-564B-BEB0-F50B4A150FF0}" name="ohne BNE-Bezug" dataDxfId="0">
       <calculatedColumnFormula>IF(Tabelle3[[#This Row],[Summe Score]]&lt;5,"x","")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{69EEEDEB-9D00-BA46-8FD8-CF2615F8C1FF}" name="Reflexionstiefe"/>

--- a/25-11-pdf-Analyzer/analyse_ergebnisse_v4-Mathbuch1.xlsx
+++ b/25-11-pdf-Analyzer/analyse_ergebnisse_v4-Mathbuch1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/131a8beddc4e0454/01JupyterAndCo/04GitHub/GitHubCloneMBP/richard4231.github.io/25-11-pdf-Analyzer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="356" documentId="8_{520C6DA0-CDB0-624A-9949-4D5B6898A185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07ED0D91-A0C6-D445-869C-2564EB5D5513}"/>
+  <xr:revisionPtr revIDLastSave="399" documentId="8_{520C6DA0-CDB0-624A-9949-4D5B6898A185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3BE080C4-66B0-0C47-ADA5-B9BB93753608}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="27040" windowHeight="16960" xr2:uid="{F946418D-52D0-4E49-9A8C-9784AA1B6916}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="27040" windowHeight="16960" xr2:uid="{F946418D-52D0-4E49-9A8C-9784AA1B6916}"/>
   </bookViews>
   <sheets>
     <sheet name="analyse_ergebnisse_v4-Mathbuch1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6444" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6340" uniqueCount="168">
   <si>
     <t>PDF</t>
   </si>
@@ -510,9 +510,6 @@
     <t>Grössen</t>
   </si>
   <si>
-    <t>(x)</t>
-  </si>
-  <si>
     <t>Graphen, Geschwindigkeit</t>
   </si>
   <si>
@@ -555,10 +552,16 @@
     <t>Pasta</t>
   </si>
   <si>
-    <t>ohne BNE-Bezug</t>
+    <t>Reflexionstiefe</t>
   </si>
   <si>
-    <t>Reflexionstiefe</t>
+    <t>Stufe BNE-Bezug</t>
+  </si>
+  <si>
+    <t>Stufe 0</t>
+  </si>
+  <si>
+    <t>Total</t>
   </si>
 </sst>
 </file>
@@ -1014,7 +1017,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -1057,13 +1060,15 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20 % - Akzent1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20 % - Akzent2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20 % - Akzent3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -1096,6 +1101,7 @@
     <cellStyle name="Gut" xfId="6" builtinId="26" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Notiz" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Prozent" xfId="42" builtinId="5"/>
     <cellStyle name="Schlecht" xfId="7" builtinId="27" customBuiltin="1"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
     <cellStyle name="Überschrift" xfId="1" builtinId="15" customBuiltin="1"/>
@@ -1107,10 +1113,7 @@
     <cellStyle name="Warnender Text" xfId="14" builtinId="11" customBuiltin="1"/>
     <cellStyle name="Zelle überprüfen" xfId="13" builtinId="23" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
+  <dxfs count="3">
     <dxf>
       <numFmt numFmtId="164" formatCode="0.0"/>
     </dxf>
@@ -1165,8 +1168,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{3E2130B6-01EB-504A-A82F-116D857DC737}" name="Tabelle3" displayName="Tabelle3" ref="V1:AE113" totalsRowShown="0">
-  <autoFilter ref="V1:AE113" xr:uid="{3E2130B6-01EB-504A-A82F-116D857DC737}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{3E2130B6-01EB-504A-A82F-116D857DC737}" name="Tabelle3" displayName="Tabelle3" ref="V1:AC113" totalsRowShown="0">
+  <autoFilter ref="V1:AC113" xr:uid="{3E2130B6-01EB-504A-A82F-116D857DC737}">
     <filterColumn colId="1">
       <filters>
         <filter val="1"/>
@@ -1283,25 +1286,21 @@
       </filters>
     </filterColumn>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="V2:AD108">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="V2:AB108">
     <sortCondition descending="1" ref="Z1:Z113"/>
   </sortState>
-  <tableColumns count="10">
+  <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{A0C018C7-F6D1-F841-810B-8A6360183DC9}" name="Seite"/>
-    <tableColumn id="11" xr3:uid="{E0FED4AD-0AF3-6D4D-82A4-118DC92CC3B4}" name="Schulbuchseite" dataDxfId="3">
+    <tableColumn id="11" xr3:uid="{E0FED4AD-0AF3-6D4D-82A4-118DC92CC3B4}" name="Schulbuchseite" dataDxfId="2">
       <calculatedColumnFormula>Tabelle3[[#This Row],[Seite]]-2</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{B8F867EA-5D14-7E4C-8895-3EA33DED557A}" name="Anzahl"/>
     <tableColumn id="3" xr3:uid="{AA9B75F7-387B-2C4D-9051-47B9A42EC4A5}" name="Rang"/>
-    <tableColumn id="4" xr3:uid="{684ACF35-1508-3E48-8C5A-9F196266158C}" name="Summe Score" dataDxfId="2">
+    <tableColumn id="4" xr3:uid="{684ACF35-1508-3E48-8C5A-9F196266158C}" name="Summe Score" dataDxfId="1">
       <calculatedColumnFormula array="1">SUMPRODUCT((Tabelle1[Seite]=V2)*Tabelle1[Score_Gewichtet])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{4C63FC84-FA0F-B746-B1EA-28FD761487ED}" name="Thema" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{7A9789D8-EE21-4F46-878E-F11CD8F07DB7}" name="implizit"/>
-    <tableColumn id="6" xr3:uid="{F78D389C-6566-B34B-A4EE-4303445DEBC7}" name="explizit"/>
-    <tableColumn id="8" xr3:uid="{9066A753-44BD-564B-BEB0-F50B4A150FF0}" name="ohne BNE-Bezug" dataDxfId="0">
-      <calculatedColumnFormula>IF(Tabelle3[[#This Row],[Summe Score]]&lt;5,"x","")</calculatedColumnFormula>
-    </tableColumn>
+    <tableColumn id="9" xr3:uid="{4C63FC84-FA0F-B746-B1EA-28FD761487ED}" name="Thema" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{7A9789D8-EE21-4F46-878E-F11CD8F07DB7}" name="Stufe BNE-Bezug"/>
     <tableColumn id="7" xr3:uid="{69EEEDEB-9D00-BA46-8FD8-CF2615F8C1FF}" name="Reflexionstiefe"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1625,16 +1624,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CAE9259-8FCA-E349-9204-1C51259F460E}">
-  <dimension ref="A1:AE1569"/>
+  <dimension ref="A1:AC1569"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="8" max="8" width="14.1640625" customWidth="1"/>
     <col min="10" max="10" width="16.5" customWidth="1"/>
     <col min="11" max="11" width="17.5" customWidth="1"/>
-    <col min="29" max="29" width="4.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1696,7 +1694,7 @@
         <v>1</v>
       </c>
       <c r="W1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="X1" t="s">
         <v>143</v>
@@ -1711,19 +1709,13 @@
         <v>146</v>
       </c>
       <c r="AB1" t="s">
-        <v>138</v>
+        <v>165</v>
       </c>
       <c r="AC1" t="s">
-        <v>137</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>165</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.2">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1787,11 +1779,11 @@
         <v>33.950000000000003</v>
       </c>
       <c r="AA2" s="1"/>
-      <c r="AD2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AB2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1854,13 +1846,13 @@
         <v>47.800000000000018</v>
       </c>
       <c r="AA3" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.2">
+        <v>163</v>
+      </c>
+      <c r="AB3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -1923,11 +1915,11 @@
         <v>34.050000000000004</v>
       </c>
       <c r="AA4" s="1"/>
-      <c r="AD4" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AB4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -1990,11 +1982,11 @@
         <v>33.350000000000009</v>
       </c>
       <c r="AA5" s="1"/>
-      <c r="AD5" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AB5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -2057,11 +2049,11 @@
         <v>28.249999999999996</v>
       </c>
       <c r="AA6" s="1"/>
-      <c r="AD6" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AB6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -2124,13 +2116,13 @@
         <v>31.150000000000002</v>
       </c>
       <c r="AA7" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="AB7" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="AB7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -2193,11 +2185,11 @@
         <v>27.150000000000006</v>
       </c>
       <c r="AA8" s="1"/>
-      <c r="AD8" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AB8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -2260,11 +2252,11 @@
         <v>27.250000000000007</v>
       </c>
       <c r="AA9" s="1"/>
-      <c r="AD9" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AB9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -2327,11 +2319,11 @@
         <v>25.200000000000006</v>
       </c>
       <c r="AA10" s="1"/>
-      <c r="AD10" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AB10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -2394,11 +2386,11 @@
         <v>26.650000000000006</v>
       </c>
       <c r="AA11" s="1"/>
-      <c r="AD11" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AB11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -2461,11 +2453,11 @@
         <v>25.550000000000004</v>
       </c>
       <c r="AA12" s="1"/>
-      <c r="AD12" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AB12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -2528,11 +2520,11 @@
         <v>25.100000000000012</v>
       </c>
       <c r="AA13" s="1"/>
-      <c r="AD13" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AB13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>11</v>
       </c>
@@ -2595,13 +2587,13 @@
         <v>25.2</v>
       </c>
       <c r="AA14" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="AB14" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+        <v>152</v>
+      </c>
+      <c r="AB14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>11</v>
       </c>
@@ -2664,11 +2656,11 @@
         <v>25.050000000000004</v>
       </c>
       <c r="AA15" s="1"/>
-      <c r="AD15" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AB15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>11</v>
       </c>
@@ -2733,15 +2725,11 @@
       <c r="AA16" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="AB16" t="s">
-        <v>134</v>
-      </c>
-      <c r="AD16" t="str">
-        <f>IF(Tabelle3[[#This Row],[Summe Score]]&lt;5,"x","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>11</v>
       </c>
@@ -2804,11 +2792,11 @@
         <v>23.600000000000005</v>
       </c>
       <c r="AA17" s="1"/>
-      <c r="AD17" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>11</v>
       </c>
@@ -2873,15 +2861,11 @@
       <c r="AA18" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="AB18" t="s">
-        <v>150</v>
-      </c>
-      <c r="AD18" t="str">
-        <f>IF(Tabelle3[[#This Row],[Summe Score]]&lt;5,"x","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>11</v>
       </c>
@@ -2944,12 +2928,11 @@
         <v>23.45</v>
       </c>
       <c r="AA19" s="1"/>
-      <c r="AD19" t="str">
-        <f>IF(Tabelle3[[#This Row],[Summe Score]]&lt;5,"x","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>11</v>
       </c>
@@ -3012,16 +2995,13 @@
         <v>22.8</v>
       </c>
       <c r="AA20" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="AB20" t="s">
-        <v>134</v>
-      </c>
-      <c r="AD20" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.2">
+        <v>156</v>
+      </c>
+      <c r="AB20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>11</v>
       </c>
@@ -3084,11 +3064,11 @@
         <v>22.550000000000004</v>
       </c>
       <c r="AA21" s="1"/>
-      <c r="AD21" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>11</v>
       </c>
@@ -3151,11 +3131,11 @@
         <v>21.650000000000002</v>
       </c>
       <c r="AA22" s="1"/>
-      <c r="AD22" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>11</v>
       </c>
@@ -3218,11 +3198,11 @@
         <v>22.000000000000007</v>
       </c>
       <c r="AA23" s="1"/>
-      <c r="AD23" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="24" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>11</v>
       </c>
@@ -3285,11 +3265,11 @@
         <v>21.550000000000004</v>
       </c>
       <c r="AA24" s="1"/>
-      <c r="AD24" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="25" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>11</v>
       </c>
@@ -3352,11 +3332,11 @@
         <v>20.400000000000002</v>
       </c>
       <c r="AA25" s="1"/>
-      <c r="AD25" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="26" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>11</v>
       </c>
@@ -3419,11 +3399,11 @@
         <v>21.450000000000003</v>
       </c>
       <c r="AA26" s="1"/>
-      <c r="AD26" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="27" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>11</v>
       </c>
@@ -3486,11 +3466,11 @@
         <v>20.75</v>
       </c>
       <c r="AA27" s="1"/>
-      <c r="AD27" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="28" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>11</v>
       </c>
@@ -3553,13 +3533,13 @@
         <v>20.650000000000006</v>
       </c>
       <c r="AA28" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="AB28" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="29" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>11</v>
       </c>
@@ -3622,11 +3602,11 @@
         <v>20.55</v>
       </c>
       <c r="AA29" s="1"/>
-      <c r="AD29" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="30" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>11</v>
       </c>
@@ -3689,11 +3669,11 @@
         <v>20.450000000000006</v>
       </c>
       <c r="AA30" s="1"/>
-      <c r="AD30" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="31" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>11</v>
       </c>
@@ -3756,11 +3736,11 @@
         <v>19.750000000000004</v>
       </c>
       <c r="AA31" s="1"/>
-      <c r="AD31" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="32" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>11</v>
       </c>
@@ -3823,11 +3803,11 @@
         <v>20</v>
       </c>
       <c r="AA32" s="1"/>
-      <c r="AD32" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="33" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>11</v>
       </c>
@@ -3890,11 +3870,11 @@
         <v>19.5</v>
       </c>
       <c r="AA33" s="1"/>
-      <c r="AD33" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="34" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>11</v>
       </c>
@@ -3959,15 +3939,11 @@
       <c r="AA34" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="AB34" t="s">
-        <v>134</v>
-      </c>
-      <c r="AD34" t="str">
-        <f>IF(Tabelle3[[#This Row],[Summe Score]]&lt;5,"x","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>11</v>
       </c>
@@ -4030,11 +4006,11 @@
         <v>19.250000000000004</v>
       </c>
       <c r="AA35" s="1"/>
-      <c r="AD35" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="36" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>11</v>
       </c>
@@ -4097,11 +4073,11 @@
         <v>19.099999999999998</v>
       </c>
       <c r="AA36" s="1"/>
-      <c r="AD36" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="37" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>11</v>
       </c>
@@ -4164,11 +4140,11 @@
         <v>18.350000000000009</v>
       </c>
       <c r="AA37" s="1"/>
-      <c r="AD37" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="38" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>11</v>
       </c>
@@ -4231,17 +4207,13 @@
         <v>18.5</v>
       </c>
       <c r="AA38" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="AB38" t="s">
-        <v>150</v>
-      </c>
-      <c r="AD38" t="str">
-        <f>IF(Tabelle3[[#This Row],[Summe Score]]&lt;5,"x","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" spans="1:30" x14ac:dyDescent="0.2">
+        <v>157</v>
+      </c>
+      <c r="AB38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>11</v>
       </c>
@@ -4304,13 +4276,13 @@
         <v>17.850000000000005</v>
       </c>
       <c r="AA39" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="AD39" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="40" spans="1:30" x14ac:dyDescent="0.2">
+        <v>161</v>
+      </c>
+      <c r="AB39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>11</v>
       </c>
@@ -4373,11 +4345,11 @@
         <v>17.950000000000003</v>
       </c>
       <c r="AA40" s="1"/>
-      <c r="AD40" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="41" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>11</v>
       </c>
@@ -4440,11 +4412,11 @@
         <v>17.700000000000003</v>
       </c>
       <c r="AA41" s="1"/>
-      <c r="AD41" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="42" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>11</v>
       </c>
@@ -4507,11 +4479,11 @@
         <v>17.800000000000004</v>
       </c>
       <c r="AA42" s="1"/>
-      <c r="AD42" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="43" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>11</v>
       </c>
@@ -4574,11 +4546,11 @@
         <v>17.500000000000007</v>
       </c>
       <c r="AA43" s="1"/>
-      <c r="AD43" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="44" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>11</v>
       </c>
@@ -4641,11 +4613,11 @@
         <v>17.500000000000004</v>
       </c>
       <c r="AA44" s="1"/>
-      <c r="AD44" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="45" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>11</v>
       </c>
@@ -4708,11 +4680,11 @@
         <v>16.850000000000001</v>
       </c>
       <c r="AA45" s="1"/>
-      <c r="AD45" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="46" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>11</v>
       </c>
@@ -4775,11 +4747,11 @@
         <v>15.499999999999998</v>
       </c>
       <c r="AA46" s="1"/>
-      <c r="AD46" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="47" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>11</v>
       </c>
@@ -4842,11 +4814,11 @@
         <v>16.7</v>
       </c>
       <c r="AA47" s="1"/>
-      <c r="AD47" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="48" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>11</v>
       </c>
@@ -4909,11 +4881,11 @@
         <v>16.500000000000004</v>
       </c>
       <c r="AA48" s="1"/>
-      <c r="AD48" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="49" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>11</v>
       </c>
@@ -4976,17 +4948,13 @@
         <v>15.95</v>
       </c>
       <c r="AA49" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="AB49" t="s">
-        <v>150</v>
-      </c>
-      <c r="AD49" t="str">
-        <f>IF(Tabelle3[[#This Row],[Summe Score]]&lt;5,"x","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50" spans="1:30" x14ac:dyDescent="0.2">
+        <v>153</v>
+      </c>
+      <c r="AB49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>11</v>
       </c>
@@ -5049,13 +5017,13 @@
         <v>15.599999999999998</v>
       </c>
       <c r="AA50" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="AB50" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="51" spans="1:30" x14ac:dyDescent="0.2">
+        <v>159</v>
+      </c>
+      <c r="AB50">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>11</v>
       </c>
@@ -5118,11 +5086,11 @@
         <v>15</v>
       </c>
       <c r="AA51" s="1"/>
-      <c r="AD51" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="52" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>11</v>
       </c>
@@ -5185,17 +5153,13 @@
         <v>15.499999999999998</v>
       </c>
       <c r="AA52" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="AB52" t="s">
-        <v>134</v>
-      </c>
-      <c r="AD52" t="str">
-        <f>IF(Tabelle3[[#This Row],[Summe Score]]&lt;5,"x","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53" spans="1:30" x14ac:dyDescent="0.2">
+        <v>158</v>
+      </c>
+      <c r="AB52">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>11</v>
       </c>
@@ -5258,11 +5222,11 @@
         <v>15.1</v>
       </c>
       <c r="AA53" s="1"/>
-      <c r="AD53" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="54" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>11</v>
       </c>
@@ -5325,11 +5289,11 @@
         <v>14.95</v>
       </c>
       <c r="AA54" s="1"/>
-      <c r="AD54" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="55" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>11</v>
       </c>
@@ -5392,17 +5356,13 @@
         <v>14.499999999999996</v>
       </c>
       <c r="AA55" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="AB55" t="s">
-        <v>150</v>
-      </c>
-      <c r="AD55" t="str">
-        <f>IF(Tabelle3[[#This Row],[Summe Score]]&lt;5,"x","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56" spans="1:30" x14ac:dyDescent="0.2">
+        <v>155</v>
+      </c>
+      <c r="AB55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>11</v>
       </c>
@@ -5465,11 +5425,11 @@
         <v>14.799999999999999</v>
       </c>
       <c r="AA56" s="1"/>
-      <c r="AD56" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="57" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>11</v>
       </c>
@@ -5532,11 +5492,11 @@
         <v>14.799999999999995</v>
       </c>
       <c r="AA57" s="1"/>
-      <c r="AD57" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="58" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>11</v>
       </c>
@@ -5599,11 +5559,11 @@
         <v>14.45</v>
       </c>
       <c r="AA58" s="1"/>
-      <c r="AD58" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="59" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>11</v>
       </c>
@@ -5668,15 +5628,11 @@
       <c r="AA59" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="AB59" t="s">
-        <v>134</v>
-      </c>
-      <c r="AD59" t="str">
-        <f>IF(Tabelle3[[#This Row],[Summe Score]]&lt;5,"x","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB59">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>11</v>
       </c>
@@ -5739,13 +5695,13 @@
         <v>14.35</v>
       </c>
       <c r="AA60" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="AB60" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="61" spans="1:30" x14ac:dyDescent="0.2">
+        <v>152</v>
+      </c>
+      <c r="AB60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>11</v>
       </c>
@@ -5808,11 +5764,11 @@
         <v>13.049999999999999</v>
       </c>
       <c r="AA61" s="1"/>
-      <c r="AD61" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="62" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>11</v>
       </c>
@@ -5875,11 +5831,11 @@
         <v>13.099999999999998</v>
       </c>
       <c r="AA62" s="1"/>
-      <c r="AD62" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="63" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>11</v>
       </c>
@@ -5942,11 +5898,11 @@
         <v>11.85</v>
       </c>
       <c r="AA63" s="1"/>
-      <c r="AD63" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="64" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>11</v>
       </c>
@@ -6009,13 +5965,13 @@
         <v>12.9</v>
       </c>
       <c r="AA64" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="AB64" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="65" spans="1:30" x14ac:dyDescent="0.2">
+        <v>157</v>
+      </c>
+      <c r="AB64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>11</v>
       </c>
@@ -6078,17 +6034,13 @@
         <v>12.799999999999999</v>
       </c>
       <c r="AA65" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="AB65" t="s">
-        <v>150</v>
-      </c>
-      <c r="AD65" t="str">
-        <f>IF(Tabelle3[[#This Row],[Summe Score]]&lt;5,"x","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66" spans="1:30" x14ac:dyDescent="0.2">
+        <v>153</v>
+      </c>
+      <c r="AB65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>11</v>
       </c>
@@ -6151,11 +6103,11 @@
         <v>12.799999999999995</v>
       </c>
       <c r="AA66" s="1"/>
-      <c r="AD66" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="67" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>11</v>
       </c>
@@ -6218,11 +6170,11 @@
         <v>12.349999999999998</v>
       </c>
       <c r="AA67" s="1"/>
-      <c r="AD67" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="68" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>11</v>
       </c>
@@ -6285,11 +6237,11 @@
         <v>12.149999999999997</v>
       </c>
       <c r="AA68" s="1"/>
-      <c r="AD68" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="69" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>11</v>
       </c>
@@ -6352,11 +6304,11 @@
         <v>11.649999999999999</v>
       </c>
       <c r="AA69" s="1"/>
-      <c r="AD69" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="70" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>11</v>
       </c>
@@ -6419,11 +6371,11 @@
         <v>11.799999999999999</v>
       </c>
       <c r="AA70" s="1"/>
-      <c r="AD70" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="71" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>11</v>
       </c>
@@ -6486,13 +6438,13 @@
         <v>11.55</v>
       </c>
       <c r="AA71" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="AB71" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="72" spans="1:30" x14ac:dyDescent="0.2">
+        <v>154</v>
+      </c>
+      <c r="AB71">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>11</v>
       </c>
@@ -6555,11 +6507,11 @@
         <v>10.899999999999997</v>
       </c>
       <c r="AA72" s="1"/>
-      <c r="AD72" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="73" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>11</v>
       </c>
@@ -6622,11 +6574,11 @@
         <v>11.549999999999999</v>
       </c>
       <c r="AA73" s="1"/>
-      <c r="AD73" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="74" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>11</v>
       </c>
@@ -6689,11 +6641,11 @@
         <v>10.95</v>
       </c>
       <c r="AA74" s="1"/>
-      <c r="AD74" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="75" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>11</v>
       </c>
@@ -6756,11 +6708,11 @@
         <v>10.7</v>
       </c>
       <c r="AA75" s="1"/>
-      <c r="AD75" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="76" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>11</v>
       </c>
@@ -6823,13 +6775,13 @@
         <v>10.599999999999996</v>
       </c>
       <c r="AA76" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="AB76" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="77" spans="1:30" x14ac:dyDescent="0.2">
+        <v>160</v>
+      </c>
+      <c r="AB76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>11</v>
       </c>
@@ -6892,11 +6844,11 @@
         <v>10.65</v>
       </c>
       <c r="AA77" s="1"/>
-      <c r="AD77" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="78" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>11</v>
       </c>
@@ -6959,11 +6911,11 @@
         <v>10.199999999999999</v>
       </c>
       <c r="AA78" s="1"/>
-      <c r="AD78" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="79" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>11</v>
       </c>
@@ -7026,11 +6978,11 @@
         <v>10.449999999999998</v>
       </c>
       <c r="AA79" s="1"/>
-      <c r="AD79" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="80" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>11</v>
       </c>
@@ -7095,15 +7047,11 @@
       <c r="AA80" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="AB80" t="s">
-        <v>134</v>
-      </c>
-      <c r="AD80" t="str">
-        <f>IF(Tabelle3[[#This Row],[Summe Score]]&lt;5,"x","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="81" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB80">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>11</v>
       </c>
@@ -7166,11 +7114,11 @@
         <v>9.0499999999999989</v>
       </c>
       <c r="AA81" s="1"/>
-      <c r="AD81" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="82" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>11</v>
       </c>
@@ -7233,11 +7181,11 @@
         <v>9.6999999999999993</v>
       </c>
       <c r="AA82" s="1"/>
-      <c r="AD82" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="83" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>11</v>
       </c>
@@ -7300,11 +7248,11 @@
         <v>9.4499999999999993</v>
       </c>
       <c r="AA83" s="1"/>
-      <c r="AD83" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="84" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>11</v>
       </c>
@@ -7367,11 +7315,11 @@
         <v>8.1</v>
       </c>
       <c r="AA84" s="1"/>
-      <c r="AD84" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="85" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>11</v>
       </c>
@@ -7434,11 +7382,11 @@
         <v>8.3999999999999986</v>
       </c>
       <c r="AA85" s="1"/>
-      <c r="AD85" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="86" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>11</v>
       </c>
@@ -7501,17 +7449,13 @@
         <v>8.35</v>
       </c>
       <c r="AA86" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="AB86" t="s">
-        <v>134</v>
-      </c>
-      <c r="AD86" t="str">
-        <f>IF(Tabelle3[[#This Row],[Summe Score]]&lt;5,"x","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="87" spans="1:30" x14ac:dyDescent="0.2">
+        <v>154</v>
+      </c>
+      <c r="AB86">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>11</v>
       </c>
@@ -7574,11 +7518,11 @@
         <v>7.7</v>
       </c>
       <c r="AA87" s="1"/>
-      <c r="AD87" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="88" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>11</v>
       </c>
@@ -7641,17 +7585,13 @@
         <v>7.9499999999999993</v>
       </c>
       <c r="AA88" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="AB88" t="s">
-        <v>150</v>
-      </c>
-      <c r="AD88" t="str">
-        <f>IF(Tabelle3[[#This Row],[Summe Score]]&lt;5,"x","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="89" spans="1:30" x14ac:dyDescent="0.2">
+        <v>155</v>
+      </c>
+      <c r="AB88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>11</v>
       </c>
@@ -7714,11 +7654,11 @@
         <v>7.3</v>
       </c>
       <c r="AA89" s="1"/>
-      <c r="AD89" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="90" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>11</v>
       </c>
@@ -7781,11 +7721,11 @@
         <v>7.6</v>
       </c>
       <c r="AA90" s="1"/>
-      <c r="AD90" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="91" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>11</v>
       </c>
@@ -7848,11 +7788,11 @@
         <v>7.4499999999999993</v>
       </c>
       <c r="AA91" s="1"/>
-      <c r="AD91" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="92" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>11</v>
       </c>
@@ -7915,11 +7855,11 @@
         <v>5.049999999999998</v>
       </c>
       <c r="AA92" s="1"/>
-      <c r="AD92" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="93" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>11</v>
       </c>
@@ -7982,11 +7922,11 @@
         <v>7.2999999999999989</v>
       </c>
       <c r="AA93" s="1"/>
-      <c r="AD93" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="94" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>11</v>
       </c>
@@ -8049,11 +7989,11 @@
         <v>7.05</v>
       </c>
       <c r="AA94" s="1"/>
-      <c r="AD94" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="95" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>11</v>
       </c>
@@ -8116,11 +8056,11 @@
         <v>6.6999999999999993</v>
       </c>
       <c r="AA95" s="1"/>
-      <c r="AD95" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="96" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>11</v>
       </c>
@@ -8183,11 +8123,11 @@
         <v>6.6499999999999986</v>
       </c>
       <c r="AA96" s="1"/>
-      <c r="AD96" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="97" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>11</v>
       </c>
@@ -8252,15 +8192,11 @@
       <c r="AA97" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="AB97" t="s">
-        <v>134</v>
-      </c>
-      <c r="AD97" t="str">
-        <f>IF(Tabelle3[[#This Row],[Summe Score]]&lt;5,"x","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="98" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB97">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>11</v>
       </c>
@@ -8323,11 +8259,11 @@
         <v>6.3999999999999995</v>
       </c>
       <c r="AA98" s="1"/>
-      <c r="AD98" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="99" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>11</v>
       </c>
@@ -8390,11 +8326,11 @@
         <v>6.35</v>
       </c>
       <c r="AA99" s="1"/>
-      <c r="AD99" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="100" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>11</v>
       </c>
@@ -8457,11 +8393,11 @@
         <v>5.6499999999999986</v>
       </c>
       <c r="AA100" s="1"/>
-      <c r="AD100" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="101" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>11</v>
       </c>
@@ -8524,11 +8460,11 @@
         <v>5.1999999999999984</v>
       </c>
       <c r="AA101" s="1"/>
-      <c r="AD101" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="102" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>11</v>
       </c>
@@ -8591,11 +8527,11 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="AA102" s="1"/>
-      <c r="AD102" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="103" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>11</v>
       </c>
@@ -8658,11 +8594,11 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="AA103" s="1"/>
-      <c r="AD103" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="104" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>11</v>
       </c>
@@ -8725,13 +8661,13 @@
         <v>4.6999999999999993</v>
       </c>
       <c r="AA104" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="AB104" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="105" spans="1:30" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="AB104">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>11</v>
       </c>
@@ -8794,11 +8730,11 @@
         <v>5</v>
       </c>
       <c r="AA105" s="1"/>
-      <c r="AD105" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="106" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>11</v>
       </c>
@@ -8861,11 +8797,11 @@
         <v>4.1499999999999995</v>
       </c>
       <c r="AA106" s="1"/>
-      <c r="AD106" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="107" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>11</v>
       </c>
@@ -8928,11 +8864,11 @@
         <v>4.05</v>
       </c>
       <c r="AA107" s="1"/>
-      <c r="AD107" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="108" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>11</v>
       </c>
@@ -8995,12 +8931,11 @@
         <v>0.1</v>
       </c>
       <c r="AA108" s="1"/>
-      <c r="AD108" t="str">
-        <f>IF(Tabelle3[[#This Row],[Summe Score]]&lt;5,"x","")</f>
-        <v>x</v>
-      </c>
-    </row>
-    <row r="109" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>11</v>
       </c>
@@ -9063,12 +8998,11 @@
         <v>4</v>
       </c>
       <c r="AA109" s="1"/>
-      <c r="AD109" t="str">
-        <f>IF(Tabelle3[[#This Row],[Summe Score]]&lt;5,"x","")</f>
-        <v>x</v>
-      </c>
-    </row>
-    <row r="110" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>11</v>
       </c>
@@ -9131,12 +9065,11 @@
         <v>3.5500000000000003</v>
       </c>
       <c r="AA110" s="1"/>
-      <c r="AD110" t="str">
-        <f>IF(Tabelle3[[#This Row],[Summe Score]]&lt;5,"x","")</f>
-        <v>x</v>
-      </c>
-    </row>
-    <row r="111" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>11</v>
       </c>
@@ -9199,12 +9132,11 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="AA111" s="1"/>
-      <c r="AD111" t="str">
-        <f>IF(Tabelle3[[#This Row],[Summe Score]]&lt;5,"x","")</f>
-        <v>x</v>
-      </c>
-    </row>
-    <row r="112" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>11</v>
       </c>
@@ -9267,12 +9199,11 @@
         <v>0.79999999999999993</v>
       </c>
       <c r="AA112" s="1"/>
-      <c r="AD112" t="str">
-        <f>IF(Tabelle3[[#This Row],[Summe Score]]&lt;5,"x","")</f>
-        <v>x</v>
-      </c>
-    </row>
-    <row r="113" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AB112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>11</v>
       </c>
@@ -9335,13 +9266,13 @@
         <v>0.79999999999999993</v>
       </c>
       <c r="AA113" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="AB113" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="114" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AB113">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>11</v>
       </c>
@@ -9376,7 +9307,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="115" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>11</v>
       </c>
@@ -9410,12 +9341,22 @@
       <c r="K115">
         <v>3.75</v>
       </c>
+      <c r="Z115">
+        <v>3</v>
+      </c>
+      <c r="AA115" t="s">
+        <v>24</v>
+      </c>
       <c r="AB115">
-        <f>COUNTA(AB3:AB113)</f>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="116" spans="1:28" x14ac:dyDescent="0.2">
+        <f>COUNTIF(Tabelle3[Stufe BNE-Bezug],Z115)</f>
+        <v>0</v>
+      </c>
+      <c r="AC115" s="3">
+        <f>AB115/AB$119</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>11</v>
       </c>
@@ -9449,8 +9390,22 @@
       <c r="K116">
         <v>1</v>
       </c>
-    </row>
-    <row r="117" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z116">
+        <v>2</v>
+      </c>
+      <c r="AA116" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB116">
+        <f>COUNTIF(Tabelle3[Stufe BNE-Bezug],Z116)</f>
+        <v>12</v>
+      </c>
+      <c r="AC116" s="3">
+        <f t="shared" ref="AC116:AC118" si="4">AB116/AB$119</f>
+        <v>0.10714285714285714</v>
+      </c>
+    </row>
+    <row r="117" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>11</v>
       </c>
@@ -9484,8 +9439,22 @@
       <c r="K117">
         <v>0.6</v>
       </c>
-    </row>
-    <row r="118" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z117">
+        <v>1</v>
+      </c>
+      <c r="AA117" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB117">
+        <f>COUNTIF(Tabelle3[Stufe BNE-Bezug],Z117)</f>
+        <v>13</v>
+      </c>
+      <c r="AC117" s="3">
+        <f t="shared" si="4"/>
+        <v>0.11607142857142858</v>
+      </c>
+    </row>
+    <row r="118" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>11</v>
       </c>
@@ -9519,8 +9488,22 @@
       <c r="K118">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="119" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z118">
+        <v>0</v>
+      </c>
+      <c r="AA118" t="s">
+        <v>166</v>
+      </c>
+      <c r="AB118">
+        <f>COUNTIF(Tabelle3[Stufe BNE-Bezug],Z118)</f>
+        <v>87</v>
+      </c>
+      <c r="AC118" s="3">
+        <f t="shared" si="4"/>
+        <v>0.7767857142857143</v>
+      </c>
+    </row>
+    <row r="119" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>11</v>
       </c>
@@ -9554,8 +9537,15 @@
       <c r="K119">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="120" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AA119" t="s">
+        <v>167</v>
+      </c>
+      <c r="AB119">
+        <f>SUM(AB115:AB118)</f>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="120" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>11</v>
       </c>
@@ -9590,7 +9580,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="121" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>11</v>
       </c>
@@ -9625,7 +9615,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="122" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>11</v>
       </c>
@@ -9660,7 +9650,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="123" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>11</v>
       </c>
@@ -9695,7 +9685,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="124" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>11</v>
       </c>
@@ -9730,7 +9720,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="125" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>11</v>
       </c>
@@ -9765,7 +9755,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="126" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>11</v>
       </c>
@@ -9800,7 +9790,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="127" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>11</v>
       </c>
@@ -9835,7 +9825,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="128" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>11</v>
       </c>
@@ -60337,6 +60327,16 @@
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
+  <conditionalFormatting sqref="AB2:AB113">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.78740157499999996" right="0.78740157499999996" top="0.984251969" bottom="0.984251969" header="0.4921259845" footer="0.4921259845"/>
   <tableParts count="2">
     <tablePart r:id="rId1"/>
